--- a/NMR_Impurities.xlsx
+++ b/NMR_Impurities.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/pwljus001_myuct_ac_za/Documents/6_UCT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="690" documentId="8_{AC23EF29-69B1-4E04-896D-74A284261976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E1D7F3B-FB80-48AD-91BE-638AEB56B169}"/>
+  <xr:revisionPtr revIDLastSave="692" documentId="8_{AC23EF29-69B1-4E04-896D-74A284261976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5168382-FA1E-4EE7-ABB1-36CF91F1AAB3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Peak Matcher" sheetId="6" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="134">
   <si>
     <t>Type</t>
   </si>
@@ -723,6 +723,9 @@
       </rPr>
       <t>O</t>
     </r>
+  </si>
+  <si>
+    <t>THF-d8</t>
   </si>
 </sst>
 </file>
@@ -970,6 +973,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -979,16 +989,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1307,40 +1310,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="F1" s="19" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="F1" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18" t="s">
+      <c r="H2" s="15"/>
+      <c r="I2" s="15" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1349,10 +1352,10 @@
         <v>2.5</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>3</v>
+        <v>133</v>
       </c>
       <c r="C3" s="9">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>4</v>
@@ -1369,14 +1372,14 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="14"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="16"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="16"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="19"/>
     </row>
     <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
@@ -1406,7 +1409,7 @@
     </row>
     <row r="6" spans="1:9" s="7" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="str" cm="1">
-        <f t="array" ref="A6:D15">_xlfn.LET(
+        <f t="array" ref="A6:D8">_xlfn.LET(
   _xlpm.solventCol, MATCH(B3, 'Shift Table'!D1:Z1, 0),
   _xlpm.rawVals, INDEX('Shift Table'!D2:Z1000,, _xlpm.solventCol),
   _xlpm.ppmValues, IFERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(_xlpm.rawVals,"−","-")),""),
@@ -1417,16 +1420,16 @@
     "No matches"
   )
 )</f>
-        <v>solvent residual signals</v>
-      </c>
-      <c r="B6" s="7">
-        <v>0</v>
+        <v>water</v>
+      </c>
+      <c r="B6" s="7" t="str">
+        <v>OH</v>
       </c>
       <c r="C6" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="D6" s="7">
-        <v>0</v>
+        <v>2.46</v>
+      </c>
+      <c r="D6" s="7" t="str">
+        <v>s</v>
       </c>
       <c r="F6" s="7" t="str" cm="1">
         <f t="array" ref="F6:I6">_xlfn.LET(
@@ -1454,130 +1457,39 @@
     </row>
     <row r="7" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="str">
-        <v>acetone</v>
+        <v>HMPA</v>
       </c>
       <c r="B7" s="7" t="str">
         <v>CH3</v>
       </c>
       <c r="C7" s="7">
-        <v>2.09</v>
+        <v>2.58</v>
       </c>
       <c r="D7" s="7" t="str">
-        <v>s</v>
+        <v>d,9.5</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="str">
-        <v>acetonitrile</v>
+        <v>triethylamine</v>
       </c>
       <c r="B8" s="7" t="str">
-        <v>CH3</v>
+        <v>CH2</v>
       </c>
       <c r="C8" s="7">
-        <v>2.0699999999999998</v>
+        <v>2.46</v>
       </c>
       <c r="D8" s="7" t="str">
-        <v>s</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="str">
-        <v>dimethylformamide</v>
-      </c>
-      <c r="B9" s="7" t="str">
-        <v>CH3</v>
-      </c>
-      <c r="C9" s="7">
-        <v>2.89</v>
-      </c>
-      <c r="D9" s="7" t="str">
-        <v>s</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="str">
-        <v>dimethylformamide</v>
-      </c>
-      <c r="B10" s="7" t="str">
-        <v>CH3</v>
-      </c>
-      <c r="C10" s="7">
-        <v>2.73</v>
-      </c>
-      <c r="D10" s="7" t="str">
-        <v>s</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="str">
-        <v>hexamethylbenzene</v>
-      </c>
-      <c r="B11" s="7" t="str">
-        <v>CH3</v>
-      </c>
-      <c r="C11" s="7">
-        <v>2.14</v>
-      </c>
-      <c r="D11" s="7" t="str">
-        <v>s</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="str">
-        <v>HMPA</v>
-      </c>
-      <c r="B12" s="7" t="str">
-        <v>CH3</v>
-      </c>
-      <c r="C12" s="7">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="D12" s="7" t="str">
-        <v>d,9.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="str">
-        <v>pyrrolidine</v>
-      </c>
-      <c r="B13" s="7" t="str">
-        <v>CH2(2,5)</v>
-      </c>
-      <c r="C13" s="7">
-        <v>2.67</v>
-      </c>
-      <c r="D13" s="7" t="str">
-        <v>m</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="str">
-        <v>toluene</v>
-      </c>
-      <c r="B14" s="7" t="str">
-        <v>CH3</v>
-      </c>
-      <c r="C14" s="7">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="D14" s="7" t="str">
-        <v>s</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="str">
-        <v>triethylamine</v>
-      </c>
-      <c r="B15" s="7" t="str">
-        <v>CH2</v>
-      </c>
-      <c r="C15" s="7">
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="D15" s="7" t="str">
         <v>q,7</v>
       </c>
     </row>
+    <row r="9" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="17" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="18" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -4992,7 +4904,7 @@
       <c r="K71" s="1">
         <v>0.13</v>
       </c>
-      <c r="L71" s="20" t="s">
+      <c r="L71" s="16" t="s">
         <v>115</v>
       </c>
       <c r="M71" s="1">
@@ -9320,7 +9232,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="14" t="s">
         <v>119</v>
       </c>
     </row>

--- a/NMR_Impurities.xlsx
+++ b/NMR_Impurities.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/pwljus001_myuct_ac_za/Documents/6_UCT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="692" documentId="8_{AC23EF29-69B1-4E04-896D-74A284261976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5168382-FA1E-4EE7-ABB1-36CF91F1AAB3}"/>
+  <xr:revisionPtr revIDLastSave="696" documentId="8_{AC23EF29-69B1-4E04-896D-74A284261976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5352EC0-8B8F-410C-A94E-793B0264B15B}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Peak Matcher" sheetId="6" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="133">
   <si>
     <t>Type</t>
   </si>
@@ -300,9 +300,6 @@
   </si>
   <si>
     <t>δ ppm</t>
-  </si>
-  <si>
-    <t>solvent residual signals</t>
   </si>
   <si>
     <t>water</t>
@@ -1311,13 +1308,13 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
       <c r="F1" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G1" s="20"/>
       <c r="H1" s="20"/>
@@ -1337,7 +1334,7 @@
         <v>75</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G2" s="15" t="s">
         <v>73</v>
@@ -1352,7 +1349,7 @@
         <v>2.5</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C3" s="9">
         <v>0.1</v>
@@ -1392,7 +1389,7 @@
         <v>76</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>1</v>
@@ -1404,7 +1401,7 @@
         <v>80</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="7" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.3">
@@ -1550,43 +1547,43 @@
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>79</v>
       </c>
       <c r="L1" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="Q1" s="13"/>
     </row>
@@ -1594,8 +1591,8 @@
       <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>81</v>
+      <c r="B2" s="11" t="s">
+        <v>78</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -1640,8 +1637,8 @@
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>81</v>
+      <c r="B3" s="11" t="s">
+        <v>78</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1670,8 +1667,8 @@
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>81</v>
+      <c r="B4" s="11" t="s">
+        <v>78</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -1696,8 +1693,8 @@
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>81</v>
+      <c r="B5" s="11" t="s">
+        <v>78</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -1720,8 +1717,8 @@
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>81</v>
+      <c r="B6" s="11" t="s">
+        <v>78</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -1743,13 +1740,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E7" s="1">
         <v>2.46</v>
@@ -1797,7 +1794,7 @@
         <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E8" s="1">
         <v>1.89</v>
@@ -1847,7 +1844,7 @@
         <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E9" s="1">
         <v>2.0499999999999998</v>
@@ -1897,7 +1894,7 @@
         <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E10" s="1">
         <v>1.95</v>
@@ -1947,7 +1944,7 @@
         <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E11" s="1">
         <v>7.31</v>
@@ -1989,13 +1986,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E12" s="1">
         <v>1.1499999999999999</v>
@@ -2039,13 +2036,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E13" s="1">
         <v>3.16</v>
@@ -2085,7 +2082,7 @@
         <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E14" s="1">
         <v>7.89</v>
@@ -2133,7 +2130,7 @@
         <v>57</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E15" s="1">
         <v>3.57</v>
@@ -2183,7 +2180,7 @@
         <v>57</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E16" s="1">
         <v>1.44</v>
@@ -2231,7 +2228,7 @@
         <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E17" s="1">
         <v>3.77</v>
@@ -2279,7 +2276,7 @@
         <v>57</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E18" s="1">
         <v>5.51</v>
@@ -2327,7 +2324,7 @@
         <v>50</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E19" s="1">
         <v>1.1200000000000001</v>
@@ -2377,7 +2374,7 @@
         <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E20" s="1">
         <v>3.38</v>
@@ -2427,7 +2424,7 @@
         <v>57</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E21" s="1">
         <v>3.43</v>
@@ -2477,7 +2474,7 @@
         <v>57</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E22" s="1">
         <v>3.53</v>
@@ -2524,10 +2521,10 @@
         <v>21</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E23" s="1">
         <v>3.28</v>
@@ -2577,7 +2574,7 @@
         <v>52</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E24" s="1">
         <v>7.91</v>
@@ -2627,7 +2624,7 @@
         <v>50</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E25" s="1">
         <v>2.88</v>
@@ -2677,7 +2674,7 @@
         <v>50</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26" s="1">
         <v>2.76</v>
@@ -2727,7 +2724,7 @@
         <v>57</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E27" s="1">
         <v>3.56</v>
@@ -2777,7 +2774,7 @@
         <v>50</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E28" s="1">
         <v>3.28</v>
@@ -2827,7 +2824,7 @@
         <v>57</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E29" s="1">
         <v>3.43</v>
@@ -2877,7 +2874,7 @@
         <v>50</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E30" s="1">
         <v>0.85</v>
@@ -2927,7 +2924,7 @@
         <v>50</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E31" s="1">
         <v>1.1000000000000001</v>
@@ -2977,7 +2974,7 @@
         <v>57</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E32" s="1">
         <v>3.51</v>
@@ -3027,7 +3024,7 @@
         <v>77</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E33" s="1">
         <v>3.3</v>
@@ -3071,7 +3068,7 @@
         <v>58</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E34" s="1">
         <v>1.94</v>
@@ -3118,10 +3115,10 @@
         <v>27</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E35" s="1">
         <v>4.04</v>
@@ -3168,10 +3165,10 @@
         <v>27</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E36" s="1">
         <v>1.19</v>
@@ -3221,7 +3218,7 @@
         <v>57</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E37" s="1">
         <v>5.36</v>
@@ -3271,7 +3268,7 @@
         <v>57</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E38" s="1">
         <v>3.48</v>
@@ -3315,13 +3312,13 @@
         <v>4</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E39" s="1">
         <v>0.88</v>
@@ -3361,13 +3358,13 @@
         <v>4</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E40" s="1">
         <v>1.29</v>
@@ -3413,7 +3410,7 @@
         <v>50</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E41" s="1">
         <v>2.1800000000000002</v>
@@ -3461,7 +3458,7 @@
         <v>50</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E42" s="1">
         <v>0.89</v>
@@ -3509,7 +3506,7 @@
         <v>57</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E43" s="1">
         <v>1.29</v>
@@ -3557,7 +3554,7 @@
         <v>50</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E44" s="1">
         <v>7.0000000000000007E-2</v>
@@ -3601,13 +3598,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E45" s="1">
         <v>2.58</v>
@@ -3651,13 +3648,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E46" s="1">
         <v>4.55</v>
@@ -3705,7 +3702,7 @@
         <v>62</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E47" s="1">
         <v>7.48</v>
@@ -3755,7 +3752,7 @@
         <v>63</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E48" s="1">
         <v>6.94</v>
@@ -3805,7 +3802,7 @@
         <v>64</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E49" s="1">
         <v>0.19</v>
@@ -3855,7 +3852,7 @@
         <v>50</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E50" s="1">
         <v>3.27</v>
@@ -3905,7 +3902,7 @@
         <v>77</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E51" s="1">
         <v>3.02</v>
@@ -3945,7 +3942,7 @@
         <v>50</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E52" s="1">
         <v>4.3099999999999996</v>
@@ -3995,7 +3992,7 @@
         <v>50</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E53" s="1">
         <v>0.89</v>
@@ -4043,7 +4040,7 @@
         <v>57</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E54" s="1">
         <v>1.31</v>
@@ -4091,7 +4088,7 @@
         <v>50</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E55" s="1">
         <v>0.9</v>
@@ -4141,7 +4138,7 @@
         <v>57</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E56" s="1">
         <v>1.33</v>
@@ -4191,7 +4188,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E57" s="1">
         <v>1.08</v>
@@ -4241,7 +4238,7 @@
         <v>52</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E58" s="1">
         <v>3.82</v>
@@ -4291,7 +4288,7 @@
         <v>50</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E59" s="1">
         <v>1.69</v>
@@ -4338,10 +4335,10 @@
         <v>41</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E60" s="1">
         <v>4.8899999999999997</v>
@@ -4388,10 +4385,10 @@
         <v>41</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E61" s="1">
         <v>4.99</v>
@@ -4441,7 +4438,7 @@
         <v>52</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E62" s="1">
         <v>5.79</v>
@@ -4491,7 +4488,7 @@
         <v>67</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E63" s="1">
         <v>8.5399999999999991</v>
@@ -4541,7 +4538,7 @@
         <v>68</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E64" s="1">
         <v>7.25</v>
@@ -4591,7 +4588,7 @@
         <v>69</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E65" s="1">
         <v>7.65</v>
@@ -4638,10 +4635,10 @@
         <v>43</v>
       </c>
       <c r="C66" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="E66" s="1">
         <v>9.9600000000000009</v>
@@ -4685,7 +4682,7 @@
         <v>70</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E67" s="1">
         <v>6.66</v>
@@ -4735,7 +4732,7 @@
         <v>71</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E68" s="1">
         <v>6.02</v>
@@ -4779,13 +4776,13 @@
         <v>4</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E69" s="1">
         <v>2.75</v>
@@ -4827,13 +4824,13 @@
         <v>4</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E70" s="1">
         <v>1.59</v>
@@ -4881,7 +4878,7 @@
         <v>50</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E71" s="1">
         <v>0.11</v>
@@ -4905,7 +4902,7 @@
         <v>0.13</v>
       </c>
       <c r="L71" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M71" s="1">
         <v>0.08</v>
@@ -4929,7 +4926,7 @@
         <v>60</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E72" s="1">
         <v>3.62</v>
@@ -4979,7 +4976,7 @@
         <v>61</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E73" s="1">
         <v>1.79</v>
@@ -5029,7 +5026,7 @@
         <v>50</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E74" s="1">
         <v>2.31</v>
@@ -5074,10 +5071,10 @@
         <v>47</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E75" s="1">
         <v>7.1</v>
@@ -5125,7 +5122,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E76" s="1">
         <v>7.19</v>
@@ -5173,7 +5170,7 @@
         <v>50</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E77" s="1">
         <v>0.97</v>
@@ -5223,7 +5220,7 @@
         <v>57</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E78" s="1">
         <v>2.46</v>
@@ -5455,7 +5452,7 @@
         <v>49</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E85" s="1">
         <v>171.69</v>
@@ -5505,7 +5502,7 @@
         <v>50</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E86" s="1">
         <v>20.13</v>
@@ -5555,7 +5552,7 @@
         <v>49</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E87" s="1">
         <v>204.19</v>
@@ -5605,7 +5602,7 @@
         <v>50</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E88" s="1">
         <v>30.17</v>
@@ -5655,7 +5652,7 @@
         <v>51</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E89" s="1">
         <v>116.79</v>
@@ -5705,7 +5702,7 @@
         <v>50</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E90" s="1">
         <v>0.45</v>
@@ -5755,7 +5752,7 @@
         <v>52</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E91" s="1">
         <v>128.84</v>
@@ -5803,7 +5800,7 @@
         <v>53</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E92" s="1">
         <v>67.5</v>
@@ -5853,7 +5850,7 @@
         <v>53</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E93" s="1">
         <v>30.57</v>
@@ -5903,7 +5900,7 @@
         <v>54</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E94" s="1">
         <v>125.69</v>
@@ -5951,7 +5948,7 @@
         <v>55</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E95" s="1">
         <v>193.37</v>
@@ -6001,7 +5998,7 @@
         <v>56</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E96" s="1">
         <v>96.89</v>
@@ -6051,7 +6048,7 @@
         <v>52</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E97" s="1">
         <v>79.239999999999995</v>
@@ -6099,7 +6096,7 @@
         <v>57</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E98" s="1">
         <v>71.34</v>
@@ -6149,7 +6146,7 @@
         <v>57</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E99" s="1">
         <v>27.58</v>
@@ -6197,7 +6194,7 @@
         <v>57</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E100" s="1">
         <v>44.64</v>
@@ -6245,7 +6242,7 @@
         <v>57</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E101" s="1">
         <v>54.67</v>
@@ -6293,7 +6290,7 @@
         <v>50</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E102" s="1">
         <v>15.49</v>
@@ -6343,7 +6340,7 @@
         <v>57</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E103" s="1">
         <v>66.14</v>
@@ -6393,7 +6390,7 @@
         <v>50</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E104" s="1">
         <v>58.72</v>
@@ -6443,7 +6440,7 @@
         <v>57</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E105" s="1">
         <v>71.17</v>
@@ -6493,7 +6490,7 @@
         <v>57</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E106" s="1">
         <v>72.72</v>
@@ -6543,7 +6540,7 @@
         <v>52</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E107" s="1">
         <v>161.96</v>
@@ -6593,7 +6590,7 @@
         <v>50</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E108" s="1">
         <v>35.65</v>
@@ -6643,7 +6640,7 @@
         <v>50</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E109" s="1">
         <v>30.7</v>
@@ -6693,7 +6690,7 @@
         <v>57</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E110" s="1">
         <v>67.650000000000006</v>
@@ -6743,7 +6740,7 @@
         <v>50</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E111" s="1">
         <v>58.72</v>
@@ -6793,7 +6790,7 @@
         <v>57</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E112" s="1">
         <v>72.58</v>
@@ -6843,7 +6840,7 @@
         <v>50</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E113" s="1">
         <v>6.79</v>
@@ -6891,7 +6888,7 @@
         <v>50</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E114" s="1">
         <v>18.899999999999999</v>
@@ -6941,7 +6938,7 @@
         <v>57</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E115" s="1">
         <v>57.6</v>
@@ -6991,7 +6988,7 @@
         <v>58</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E116" s="1">
         <v>20.45</v>
@@ -7041,7 +7038,7 @@
         <v>49</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E117" s="1">
         <v>170.32</v>
@@ -7091,7 +7088,7 @@
         <v>57</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E118" s="1">
         <v>60.3</v>
@@ -7141,7 +7138,7 @@
         <v>50</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E119" s="1">
         <v>14.37</v>
@@ -7191,7 +7188,7 @@
         <v>57</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E120" s="1">
         <v>123.09</v>
@@ -7239,7 +7236,7 @@
         <v>57</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E121" s="1">
         <v>64.349999999999994</v>
@@ -7283,13 +7280,13 @@
         <v>5</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E122" s="1">
         <v>30.45</v>
@@ -7327,7 +7324,7 @@
         <v>59</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E123" s="1">
         <v>131.88</v>
@@ -7375,7 +7372,7 @@
         <v>50</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E124" s="1">
         <v>16.71</v>
@@ -7423,7 +7420,7 @@
         <v>50</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E125" s="1">
         <v>14.22</v>
@@ -7471,7 +7468,7 @@
         <v>60</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E126" s="1">
         <v>23.33</v>
@@ -7519,7 +7516,7 @@
         <v>61</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E127" s="1">
         <v>32.340000000000003</v>
@@ -7567,7 +7564,7 @@
         <v>50</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E128" s="1">
         <v>1.83</v>
@@ -7617,7 +7614,7 @@
         <v>50</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E129" s="1">
         <v>36.89</v>
@@ -7667,7 +7664,7 @@
         <v>62</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E130" s="1">
         <v>135.72</v>
@@ -7717,7 +7714,7 @@
         <v>63</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E131" s="1">
         <v>122.2</v>
@@ -7767,7 +7764,7 @@
         <v>64</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E132" s="1">
         <v>-4.9000000000000004</v>
@@ -7815,7 +7812,7 @@
         <v>50</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E133" s="1">
         <v>49.64</v>
@@ -7865,7 +7862,7 @@
         <v>50</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E134" s="1">
         <v>62.49</v>
@@ -7915,7 +7912,7 @@
         <v>50</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E135" s="1">
         <v>14.18</v>
@@ -7963,7 +7960,7 @@
         <v>65</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E136" s="1">
         <v>23</v>
@@ -8011,7 +8008,7 @@
         <v>66</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E137" s="1">
         <v>34.869999999999997</v>
@@ -8059,7 +8056,7 @@
         <v>50</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E138" s="1">
         <v>16.600000000000001</v>
@@ -8107,7 +8104,7 @@
         <v>57</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E139" s="1">
         <v>16.82</v>
@@ -8155,7 +8152,7 @@
         <v>50</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E140" s="1">
         <v>25.7</v>
@@ -8205,7 +8202,7 @@
         <v>52</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E141" s="1">
         <v>66.14</v>
@@ -8255,7 +8252,7 @@
         <v>50</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E142" s="1">
         <v>19.27</v>
@@ -8303,7 +8300,7 @@
         <v>57</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E143" s="1">
         <v>115.74</v>
@@ -8351,7 +8348,7 @@
         <v>52</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E144" s="1">
         <v>134.02000000000001</v>
@@ -8399,7 +8396,7 @@
         <v>67</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E145" s="1">
         <v>150.57</v>
@@ -8449,7 +8446,7 @@
         <v>68</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E146" s="1">
         <v>124.08</v>
@@ -8499,7 +8496,7 @@
         <v>69</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E147" s="1">
         <v>135.99</v>
@@ -8549,7 +8546,7 @@
         <v>70</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E148" s="1">
         <v>118.03</v>
@@ -8599,7 +8596,7 @@
         <v>71</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E149" s="1">
         <v>107.74</v>
@@ -8649,7 +8646,7 @@
         <v>60</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E150" s="1">
         <v>45.82</v>
@@ -8697,7 +8694,7 @@
         <v>61</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E151" s="1">
         <v>26.17</v>
@@ -8745,7 +8742,7 @@
         <v>50</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E152" s="1">
         <v>1.2</v>
@@ -8789,7 +8786,7 @@
         <v>60</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E153" s="1">
         <v>68.03</v>
@@ -8839,7 +8836,7 @@
         <v>61</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E154" s="1">
         <v>26.19</v>
@@ -8889,7 +8886,7 @@
         <v>50</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E155" s="1">
         <v>21.29</v>
@@ -8937,7 +8934,7 @@
         <v>72</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E156" s="1">
         <v>138.24</v>
@@ -8985,7 +8982,7 @@
         <v>67</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E157" s="1">
         <v>129.47</v>
@@ -9033,7 +9030,7 @@
         <v>68</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E158" s="1">
         <v>128.71</v>
@@ -9081,7 +9078,7 @@
         <v>69</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E159" s="1">
         <v>125.84</v>
@@ -9129,7 +9126,7 @@
         <v>50</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E160" s="1">
         <v>12.51</v>
@@ -9179,7 +9176,7 @@
         <v>57</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E161" s="1">
         <v>47.18</v>
@@ -9233,12 +9230,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
@@ -9263,7 +9260,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
@@ -9343,7 +9340,7 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
@@ -9363,12 +9360,12 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
@@ -9423,7 +9420,7 @@
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
